--- a/InputData/trans/SYVbT/cn - Start Year Vehicles by Technology.xlsx
+++ b/InputData/trans/SYVbT/cn - Start Year Vehicles by Technology.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr autoCompressPictures="0" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhlxl\Desktop\EPS\eps-china2019-smart-trans\InputData\trans\SYVbT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51976DB2-39F5-44EA-B900-87A32BEBD2F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65EE5D93-5834-4F3E-B876-808E7EDC1C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3355" yWindow="829" windowWidth="21709" windowHeight="13313" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -488,13 +488,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="###0.00_)"/>
     <numFmt numFmtId="179" formatCode="#,##0_)"/>
     <numFmt numFmtId="180" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="182" formatCode="0.000%"/>
   </numFmts>
   <fonts count="46">
     <font>
@@ -1153,7 +1154,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="212">
+  <cellStyleXfs count="213">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyProtection="0">
@@ -1432,8 +1433,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1492,6 +1496,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1501,17 +1514,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="212" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="212" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="212">
+  <cellStyles count="213">
     <cellStyle name="20% - Accent1 2" xfId="15" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="20% - Accent2 2" xfId="16" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="20% - Accent3 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -1651,6 +1657,7 @@
     <cellStyle name="Wrap" xfId="137" xr:uid="{00000000-0005-0000-0000-0000D2000000}"/>
     <cellStyle name="Wrap Bold" xfId="138" xr:uid="{00000000-0005-0000-0000-0000D3000000}"/>
     <cellStyle name="Wrap Title" xfId="139" xr:uid="{00000000-0005-0000-0000-0000D4000000}"/>
+    <cellStyle name="百分比" xfId="212" builtinId="5"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="超链接" xfId="146" builtinId="8" hidden="1"/>
     <cellStyle name="超链接" xfId="140" builtinId="8" hidden="1"/>
@@ -2200,7 +2207,7 @@
       <c r="K4" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="L4" s="29"/>
+      <c r="L4" s="32"/>
     </row>
     <row r="5" spans="2:12">
       <c r="B5" s="15"/>
@@ -2213,7 +2220,7 @@
       <c r="I5" s="11"/>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
-      <c r="L5" s="29"/>
+      <c r="L5" s="32"/>
     </row>
     <row r="6" spans="2:12" ht="38.75">
       <c r="B6" s="15" t="s">
@@ -2232,7 +2239,7 @@
       <c r="K6" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="L6" s="29"/>
+      <c r="L6" s="32"/>
     </row>
     <row r="7" spans="2:12">
       <c r="B7" s="15"/>
@@ -2396,42 +2403,42 @@
       <c r="B27" t="s">
         <v>9</v>
       </c>
-      <c r="N27" s="28"/>
-      <c r="O27" s="28"/>
-      <c r="P27" s="28"/>
-      <c r="Q27" s="28"/>
-      <c r="R27" s="28"/>
-      <c r="S27" s="28"/>
+      <c r="N27" s="31"/>
+      <c r="O27" s="31"/>
+      <c r="P27" s="31"/>
+      <c r="Q27" s="31"/>
+      <c r="R27" s="31"/>
+      <c r="S27" s="31"/>
     </row>
     <row r="28" spans="2:19" ht="13.6" customHeight="1">
       <c r="B28" t="s">
         <v>10</v>
       </c>
-      <c r="N28" s="28"/>
-      <c r="O28" s="28"/>
-      <c r="P28" s="28"/>
-      <c r="Q28" s="28"/>
-      <c r="R28" s="28"/>
-      <c r="S28" s="28"/>
+      <c r="N28" s="31"/>
+      <c r="O28" s="31"/>
+      <c r="P28" s="31"/>
+      <c r="Q28" s="31"/>
+      <c r="R28" s="31"/>
+      <c r="S28" s="31"/>
     </row>
     <row r="29" spans="2:19" ht="13.6" customHeight="1">
       <c r="B29" t="s">
         <v>11</v>
       </c>
-      <c r="N29" s="28"/>
-      <c r="O29" s="28"/>
-      <c r="P29" s="28"/>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="28"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="31"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="31"/>
+      <c r="S29" s="31"/>
     </row>
     <row r="30" spans="2:19" ht="13.6" customHeight="1">
-      <c r="N30" s="28"/>
-      <c r="O30" s="28"/>
-      <c r="P30" s="28"/>
-      <c r="Q30" s="28"/>
-      <c r="R30" s="28"/>
-      <c r="S30" s="28"/>
+      <c r="N30" s="31"/>
+      <c r="O30" s="31"/>
+      <c r="P30" s="31"/>
+      <c r="Q30" s="31"/>
+      <c r="R30" s="31"/>
+      <c r="S30" s="31"/>
     </row>
     <row r="31" spans="2:19" ht="14.3" customHeight="1">
       <c r="O31" s="8"/>
@@ -2514,44 +2521,44 @@
     </row>
     <row r="43" spans="2:19" ht="13.6" customHeight="1"/>
     <row r="45" spans="2:19" ht="13.6" customHeight="1">
-      <c r="I45" s="30" t="s">
+      <c r="I45" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="J45" s="30"/>
-      <c r="K45" s="30"/>
+      <c r="J45" s="33"/>
+      <c r="K45" s="33"/>
     </row>
     <row r="46" spans="2:19" ht="13.6" customHeight="1">
       <c r="H46" s="9"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
+      <c r="I46" s="33"/>
+      <c r="J46" s="33"/>
+      <c r="K46" s="33"/>
       <c r="L46" s="9"/>
     </row>
     <row r="47" spans="2:19">
       <c r="G47" s="9"/>
       <c r="H47" s="9"/>
-      <c r="I47" s="30"/>
-      <c r="J47" s="30"/>
-      <c r="K47" s="30"/>
+      <c r="I47" s="33"/>
+      <c r="J47" s="33"/>
+      <c r="K47" s="33"/>
       <c r="L47" s="9"/>
     </row>
     <row r="48" spans="2:19">
       <c r="G48" s="9"/>
       <c r="H48" s="9"/>
-      <c r="I48" s="30"/>
-      <c r="J48" s="30"/>
-      <c r="K48" s="30"/>
+      <c r="I48" s="33"/>
+      <c r="J48" s="33"/>
+      <c r="K48" s="33"/>
       <c r="L48" s="9"/>
     </row>
     <row r="49" spans="9:11">
-      <c r="I49" s="30"/>
-      <c r="J49" s="30"/>
-      <c r="K49" s="30"/>
+      <c r="I49" s="33"/>
+      <c r="J49" s="33"/>
+      <c r="K49" s="33"/>
     </row>
     <row r="50" spans="9:11">
-      <c r="I50" s="30"/>
-      <c r="J50" s="30"/>
-      <c r="K50" s="30"/>
+      <c r="I50" s="33"/>
+      <c r="J50" s="33"/>
+      <c r="K50" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3190,7 +3197,10 @@
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
       <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
+      <c r="J12" s="34">
+        <f>J9/SUM(B9,D9,F9,H9,J9)</f>
+        <v>3.3278140715867384E-3</v>
+      </c>
       <c r="K12" s="13"/>
       <c r="L12" s="13"/>
       <c r="M12" s="13"/>
@@ -3209,7 +3219,7 @@
       <c r="H13" s="13"/>
       <c r="I13" s="13"/>
       <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
+      <c r="K13" s="35"/>
       <c r="L13" s="13"/>
       <c r="M13" s="13"/>
       <c r="N13" s="13"/>
@@ -3275,33 +3285,33 @@
       <c r="Q16" s="13"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="32"/>
-      <c r="C17" s="33" t="s">
+      <c r="B17" s="29"/>
+      <c r="C17" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33" t="s">
+      <c r="D17" s="30"/>
+      <c r="E17" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="F17" s="33"/>
+      <c r="F17" s="30"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="33">
+      <c r="A18" s="30">
         <f>A20+B20</f>
         <v>21700</v>
       </c>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33">
+      <c r="B18" s="30"/>
+      <c r="C18" s="30">
         <v>76000</v>
       </c>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33">
+      <c r="D18" s="30"/>
+      <c r="E18" s="30">
         <v>878000</v>
       </c>
-      <c r="F18" s="33"/>
+      <c r="F18" s="30"/>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="26" t="s">
@@ -3428,29 +3438,29 @@
       </c>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="31"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31" t="s">
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="31">
+      <c r="A28" s="28">
         <v>5853</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31">
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28">
         <f>A26-A28</f>
         <v>125675</v>
       </c>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="25" t="s">
@@ -3520,7 +3530,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -4009,6 +4019,12 @@
       <c r="F19" s="21"/>
       <c r="G19" s="21"/>
       <c r="H19" s="21"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="B20">
+        <f>B13/SUM(B13:H13)</f>
+        <v>3.3278140715867384E-3</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="37" type="noConversion"/>
@@ -4532,6 +4548,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x010100BD1DE36A36CC7845A4126EF01914151E" ma:contentTypeVersion="14" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="310835f059701aa681930bc3a1715053">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c" xmlns:ns3="a06c533b-533a-4f75-b7db-110f073002e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7ba933288dd05553e9ce0f804d4dc608" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -4765,15 +4790,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -4784,6 +4800,24 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2182DF7-646D-4589-A629-CF484F739AB6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="a06c533b-533a-4f75-b7db-110f073002e4"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{186E742B-F707-4292-AB4B-BBCC3EF7A9CD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4803,24 +4837,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2182DF7-646D-4589-A629-CF484F739AB6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="a06c533b-533a-4f75-b7db-110f073002e4"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A426CBD0-2BC4-4D82-AA23-473F471AA302}">
   <ds:schemaRefs>
